--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BCGcalc/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF49C751-8791-4BCD-BD60-C78962984F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{AF49C751-8791-4BCD-BD60-C78962984F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FE13902-9C77-4613-8EA7-FDB502FFD733}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="177">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -652,6 +652,54 @@
   </si>
   <si>
     <t>Add flags for FL BCG</t>
+  </si>
+  <si>
+    <t>Added flags for GP BCG</t>
+  </si>
+  <si>
+    <t>GP_Fish_BCG</t>
+  </si>
+  <si>
+    <t>Small_47c</t>
+  </si>
+  <si>
+    <t>Large_47c</t>
+  </si>
+  <si>
+    <t>Small_Not_47c</t>
+  </si>
+  <si>
+    <t>Large_Not_47c</t>
+  </si>
+  <si>
+    <t>WsAreaSqKm</t>
+  </si>
+  <si>
+    <t>DrArea_mi2</t>
+  </si>
+  <si>
+    <t>pi_dom01</t>
+  </si>
+  <si>
+    <t>individuals, dominant 01, Large</t>
+  </si>
+  <si>
+    <t>pi_SCC</t>
+  </si>
+  <si>
+    <t>species of conservation concern, present</t>
+  </si>
+  <si>
+    <t>pi_salt</t>
+  </si>
+  <si>
+    <t>salt indicator taxa, present</t>
+  </si>
+  <si>
+    <t>pi_NPL</t>
+  </si>
+  <si>
+    <t>non-parasitic lampreys, present</t>
   </si>
 </sst>
 </file>
@@ -837,7 +885,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -861,7 +909,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -871,9 +918,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -895,7 +939,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -903,23 +947,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -968,16 +995,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -993,13 +1010,17 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A15:C18" totalsRowShown="0">
   <autoFilter ref="A15:C18" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Worksheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descriptions"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="6">
       <calculatedColumnFormula>HYPERLINK(FileName&amp;A16&amp;"!A1",A16)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1297,7 +1318,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1322,7 +1343,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>45393</v>
       </c>
     </row>
@@ -1332,7 +1353,7 @@
       </c>
       <c r="B7" s="6" t="str">
         <f ca="1">LEFT(CELL("filename",B7),FIND("]",CELL("filename",B7)))</f>
-        <v>C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\[MetricFlags.xlsx]</v>
+        <v>https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BCGcalc/inst/extdata/[MetricFlags.xlsx]</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1393,7 +1414,7 @@
       <c r="B17" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="15" t="str">
+      <c r="C17" s="14" t="str">
         <f ca="1">HYPERLINK(FileName&amp;A17&amp;"!A1",A17)</f>
         <v>meta</v>
       </c>
@@ -1411,7 +1432,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="A22" s="15">
         <v>44531</v>
       </c>
       <c r="B22" t="s">
@@ -1419,7 +1440,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
+      <c r="A23" s="15">
         <v>44532</v>
       </c>
       <c r="B23" t="s">
@@ -1442,7 +1463,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
+      <c r="A27" s="15">
         <v>44603</v>
       </c>
       <c r="B27" t="s">
@@ -1450,7 +1471,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
+      <c r="A28" s="15">
         <v>44651</v>
       </c>
       <c r="B28" t="s">
@@ -1458,7 +1479,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
+      <c r="A29" s="15">
         <v>44832</v>
       </c>
       <c r="B29" t="s">
@@ -1466,7 +1487,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
+      <c r="A30" s="15">
         <v>44845</v>
       </c>
       <c r="B30" t="s">
@@ -1474,7 +1495,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
+      <c r="A31" s="15">
         <v>44866</v>
       </c>
       <c r="B31" t="s">
@@ -1482,7 +1503,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="16">
+      <c r="A32" s="15">
         <v>44881</v>
       </c>
       <c r="B32" t="s">
@@ -1490,7 +1511,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
+      <c r="A33" s="15">
         <v>44882</v>
       </c>
       <c r="B33" t="s">
@@ -1498,7 +1519,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
+      <c r="A34" s="15">
         <v>45082</v>
       </c>
       <c r="B34" t="s">
@@ -1506,7 +1527,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
+      <c r="A35" s="15">
         <v>45082</v>
       </c>
       <c r="B35" t="s">
@@ -1529,7 +1550,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="16">
+      <c r="A39" s="15">
         <v>45083</v>
       </c>
       <c r="B39" t="s">
@@ -1542,11 +1563,19 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="16">
+      <c r="A41" s="15">
         <v>45393</v>
       </c>
       <c r="B41" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="15">
+        <v>45510</v>
+      </c>
+      <c r="B42" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1654,7 @@
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1658,10 +1687,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Sheet2" filterMode="1">
+  <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -1697,14 +1726,14 @@
       <c r="H1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="18" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -1727,16 +1756,16 @@
       <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="21" t="str">
+      <c r="I2" s="19" t="str">
         <f>B2</f>
         <v>Hi</v>
       </c>
-      <c r="J2" s="21" t="str">
+      <c r="J2" s="19" t="str">
         <f>B2</f>
         <v>Hi</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -1758,16 +1787,16 @@
       <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="str">
+      <c r="I3" s="19" t="str">
         <f t="shared" ref="I3:I66" si="0">B3</f>
         <v>Hi</v>
       </c>
-      <c r="J3" s="21" t="str">
+      <c r="J3" s="19" t="str">
         <f t="shared" ref="J3:J66" si="1">B3</f>
         <v>Hi</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -1789,16 +1818,16 @@
       <c r="G4" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="21" t="str">
+      <c r="I4" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J4" s="21" t="str">
+      <c r="J4" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>125</v>
       </c>
@@ -1820,16 +1849,16 @@
       <c r="G5" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="21" t="str">
+      <c r="I5" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J5" s="21" t="str">
+      <c r="J5" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>125</v>
       </c>
@@ -1851,16 +1880,16 @@
       <c r="G6" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="21" t="str">
+      <c r="I6" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J6" s="21" t="str">
+      <c r="J6" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -1882,16 +1911,16 @@
       <c r="G7" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="21" t="str">
+      <c r="I7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J7" s="21" t="str">
+      <c r="J7" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -1913,16 +1942,16 @@
       <c r="G8" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="21" t="str">
+      <c r="I8" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J8" s="21" t="str">
+      <c r="J8" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -1944,16 +1973,16 @@
       <c r="G9" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="21" t="str">
+      <c r="I9" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J9" s="21" t="str">
+      <c r="J9" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -1975,16 +2004,16 @@
       <c r="G10" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="21" t="str">
+      <c r="I10" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J10" s="21" t="str">
+      <c r="J10" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
@@ -1994,7 +2023,7 @@
       <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E11">
@@ -2006,16 +2035,16 @@
       <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="21" t="str">
+      <c r="I11" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J11" s="21" t="str">
+      <c r="J11" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -2037,16 +2066,16 @@
       <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="21" t="str">
+      <c r="I12" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J12" s="21" t="str">
+      <c r="J12" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -2068,16 +2097,16 @@
       <c r="G13" t="b">
         <v>1</v>
       </c>
-      <c r="I13" s="21" t="str">
+      <c r="I13" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J13" s="21" t="str">
+      <c r="J13" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>125</v>
       </c>
@@ -2099,16 +2128,16 @@
       <c r="G14" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="21" t="str">
+      <c r="I14" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J14" s="21" t="str">
+      <c r="J14" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -2130,16 +2159,16 @@
       <c r="G15" t="b">
         <v>0</v>
       </c>
-      <c r="I15" s="21" t="str">
+      <c r="I15" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J15" s="21" t="str">
+      <c r="J15" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>125</v>
       </c>
@@ -2161,16 +2190,16 @@
       <c r="G16" t="b">
         <v>0</v>
       </c>
-      <c r="I16" s="21" t="str">
+      <c r="I16" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J16" s="21" t="str">
+      <c r="J16" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -2192,16 +2221,16 @@
       <c r="G17" t="b">
         <v>0</v>
       </c>
-      <c r="I17" s="21" t="str">
+      <c r="I17" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J17" s="21" t="str">
+      <c r="J17" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>125</v>
       </c>
@@ -2223,16 +2252,16 @@
       <c r="G18" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="21" t="str">
+      <c r="I18" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J18" s="21" t="str">
+      <c r="J18" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -2254,16 +2283,16 @@
       <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="I19" s="21" t="str">
+      <c r="I19" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J19" s="21" t="str">
+      <c r="J19" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -2285,16 +2314,16 @@
       <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="I20" s="21" t="str">
+      <c r="I20" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J20" s="21" t="str">
+      <c r="J20" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -2304,7 +2333,7 @@
       <c r="C21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E21">
@@ -2316,17 +2345,17 @@
       <c r="G21" t="b">
         <v>1</v>
       </c>
-      <c r="I21" s="21" t="str">
+      <c r="I21" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J21" s="21" t="str">
+      <c r="J21" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B22" s="12" t="s">
@@ -2348,17 +2377,17 @@
       <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="I22" s="21" t="str">
+      <c r="I22" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J22" s="21" t="str">
+      <c r="J22" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="12" t="s">
@@ -2380,17 +2409,17 @@
       <c r="G23" t="b">
         <v>1</v>
       </c>
-      <c r="I23" s="21" t="str">
+      <c r="I23" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J23" s="21" t="str">
+      <c r="J23" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B24" s="12" t="s">
@@ -2412,17 +2441,17 @@
       <c r="G24" t="b">
         <v>0</v>
       </c>
-      <c r="I24" s="21" t="str">
+      <c r="I24" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J24" s="21" t="str">
+      <c r="J24" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B25" s="12" t="s">
@@ -2444,17 +2473,17 @@
       <c r="G25" t="b">
         <v>0</v>
       </c>
-      <c r="I25" s="21" t="str">
+      <c r="I25" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J25" s="21" t="str">
+      <c r="J25" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B26" s="12" t="s">
@@ -2475,17 +2504,17 @@
       <c r="G26" t="b">
         <v>0</v>
       </c>
-      <c r="I26" s="21" t="str">
+      <c r="I26" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J26" s="21" t="str">
+      <c r="J26" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B27" s="12" t="s">
@@ -2506,17 +2535,17 @@
       <c r="G27" t="b">
         <v>0</v>
       </c>
-      <c r="I27" s="21" t="str">
+      <c r="I27" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J27" s="21" t="str">
+      <c r="J27" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B28" s="12" t="s">
@@ -2537,17 +2566,17 @@
       <c r="G28" t="b">
         <v>0</v>
       </c>
-      <c r="I28" s="21" t="str">
+      <c r="I28" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J28" s="21" t="str">
+      <c r="J28" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B29" s="12" t="s">
@@ -2568,17 +2597,17 @@
       <c r="G29" t="b">
         <v>1</v>
       </c>
-      <c r="I29" s="21" t="str">
+      <c r="I29" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J29" s="21" t="str">
+      <c r="J29" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B30" s="12" t="s">
@@ -2599,17 +2628,17 @@
       <c r="G30" t="b">
         <v>1</v>
       </c>
-      <c r="I30" s="21" t="str">
+      <c r="I30" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J30" s="21" t="str">
+      <c r="J30" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B31" s="12" t="s">
@@ -2618,7 +2647,7 @@
       <c r="C31" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E31">
@@ -2630,17 +2659,17 @@
       <c r="G31" t="b">
         <v>1</v>
       </c>
-      <c r="I31" s="21" t="str">
+      <c r="I31" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Hi</v>
       </c>
-      <c r="J31" s="21" t="str">
+      <c r="J31" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Hi</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B32" t="s">
@@ -2662,17 +2691,17 @@
       <c r="G32" t="b">
         <v>1</v>
       </c>
-      <c r="I32" s="21" t="str">
+      <c r="I32" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J32" s="21" t="str">
+      <c r="J32" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B33" t="s">
@@ -2694,17 +2723,17 @@
       <c r="G33" t="b">
         <v>1</v>
       </c>
-      <c r="I33" s="21" t="str">
+      <c r="I33" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J33" s="21" t="str">
+      <c r="J33" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B34" t="s">
@@ -2726,17 +2755,17 @@
       <c r="G34" t="b">
         <v>0</v>
       </c>
-      <c r="I34" s="21" t="str">
+      <c r="I34" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J34" s="21" t="str">
+      <c r="J34" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B35" t="s">
@@ -2758,17 +2787,17 @@
       <c r="G35" t="b">
         <v>0</v>
       </c>
-      <c r="I35" s="21" t="str">
+      <c r="I35" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J35" s="21" t="str">
+      <c r="J35" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B36" t="s">
@@ -2789,17 +2818,17 @@
       <c r="G36" t="b">
         <v>0</v>
       </c>
-      <c r="I36" s="21" t="str">
+      <c r="I36" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J36" s="21" t="str">
+      <c r="J36" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B37" t="s">
@@ -2820,17 +2849,17 @@
       <c r="G37" t="b">
         <v>0</v>
       </c>
-      <c r="I37" s="21" t="str">
+      <c r="I37" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J37" s="21" t="str">
+      <c r="J37" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B38" t="s">
@@ -2851,17 +2880,17 @@
       <c r="G38" t="b">
         <v>0</v>
       </c>
-      <c r="I38" s="21" t="str">
+      <c r="I38" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J38" s="21" t="str">
+      <c r="J38" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B39" t="s">
@@ -2882,17 +2911,17 @@
       <c r="G39" t="b">
         <v>1</v>
       </c>
-      <c r="I39" s="21" t="str">
+      <c r="I39" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J39" s="21" t="str">
+      <c r="J39" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B40" t="s">
@@ -2913,17 +2942,17 @@
       <c r="G40" t="b">
         <v>1</v>
       </c>
-      <c r="I40" s="21" t="str">
+      <c r="I40" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J40" s="21" t="str">
+      <c r="J40" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B41" t="s">
@@ -2932,7 +2961,7 @@
       <c r="C41" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E41">
@@ -2944,11 +2973,11 @@
       <c r="G41" t="b">
         <v>1</v>
       </c>
-      <c r="I41" s="21" t="str">
+      <c r="I41" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Lo</v>
       </c>
-      <c r="J41" s="21" t="str">
+      <c r="J41" s="19" t="str">
         <f t="shared" si="1"/>
         <v>Lo</v>
       </c>
@@ -2975,11 +3004,11 @@
       <c r="G42" t="b">
         <v>0</v>
       </c>
-      <c r="I42" s="21" t="str">
+      <c r="I42" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J42" s="21" t="str">
+      <c r="J42" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3009,11 +3038,11 @@
       <c r="H43" t="s">
         <v>115</v>
       </c>
-      <c r="I43" s="21" t="str">
+      <c r="I43" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J43" s="21" t="str">
+      <c r="J43" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3040,11 +3069,11 @@
       <c r="G44" t="b">
         <v>0</v>
       </c>
-      <c r="I44" s="21" t="str">
+      <c r="I44" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J44" s="21" t="str">
+      <c r="J44" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3071,11 +3100,11 @@
       <c r="G45" t="b">
         <v>0</v>
       </c>
-      <c r="I45" s="21" t="str">
+      <c r="I45" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J45" s="21" t="str">
+      <c r="J45" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3102,11 +3131,11 @@
       <c r="G46" t="b">
         <v>0</v>
       </c>
-      <c r="I46" s="21" t="str">
+      <c r="I46" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J46" s="21" t="str">
+      <c r="J46" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3133,11 +3162,11 @@
       <c r="G47" t="b">
         <v>0</v>
       </c>
-      <c r="I47" s="21" t="str">
+      <c r="I47" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J47" s="21" t="str">
+      <c r="J47" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3164,11 +3193,11 @@
       <c r="G48" t="b">
         <v>0</v>
       </c>
-      <c r="I48" s="21" t="str">
+      <c r="I48" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J48" s="21" t="str">
+      <c r="J48" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3195,11 +3224,11 @@
       <c r="G49" t="b">
         <v>1</v>
       </c>
-      <c r="I49" s="21" t="str">
+      <c r="I49" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J49" s="21" t="str">
+      <c r="J49" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3226,11 +3255,11 @@
       <c r="G50" t="b">
         <v>1</v>
       </c>
-      <c r="I50" s="21" t="str">
+      <c r="I50" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J50" s="21" t="str">
+      <c r="J50" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3257,11 +3286,11 @@
       <c r="G51" t="b">
         <v>0</v>
       </c>
-      <c r="I51" s="21" t="str">
+      <c r="I51" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J51" s="21" t="str">
+      <c r="J51" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3288,11 +3317,11 @@
       <c r="G52" t="b">
         <v>0</v>
       </c>
-      <c r="I52" s="21" t="str">
+      <c r="I52" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J52" s="21" t="str">
+      <c r="J52" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3319,11 +3348,11 @@
       <c r="G53" t="b">
         <v>1</v>
       </c>
-      <c r="I53" s="21" t="str">
+      <c r="I53" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J53" s="21" t="str">
+      <c r="J53" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3341,7 +3370,7 @@
       <c r="D54" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="17">
         <v>35</v>
       </c>
       <c r="F54" t="s">
@@ -3353,11 +3382,11 @@
       <c r="H54" t="s">
         <v>110</v>
       </c>
-      <c r="I54" s="21" t="str">
+      <c r="I54" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J54" s="21" t="str">
+      <c r="J54" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3384,11 +3413,11 @@
       <c r="G55" t="b">
         <v>1</v>
       </c>
-      <c r="I55" s="21" t="str">
+      <c r="I55" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J55" s="21" t="str">
+      <c r="J55" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3415,11 +3444,11 @@
       <c r="G56" t="b">
         <v>1</v>
       </c>
-      <c r="I56" s="21" t="str">
+      <c r="I56" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J56" s="21" t="str">
+      <c r="J56" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3434,7 +3463,7 @@
       <c r="C57" t="s">
         <v>72</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="20" t="s">
         <v>96</v>
       </c>
       <c r="E57">
@@ -3446,11 +3475,11 @@
       <c r="G57" t="b">
         <v>1</v>
       </c>
-      <c r="I57" s="21" t="str">
+      <c r="I57" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J57" s="21" t="str">
+      <c r="J57" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3465,7 +3494,7 @@
       <c r="C58" t="s">
         <v>74</v>
       </c>
-      <c r="D58" s="22" t="s">
+      <c r="D58" s="20" t="s">
         <v>96</v>
       </c>
       <c r="E58">
@@ -3477,11 +3506,11 @@
       <c r="G58" t="b">
         <v>1</v>
       </c>
-      <c r="I58" s="21" t="str">
+      <c r="I58" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J58" s="21" t="str">
+      <c r="J58" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3496,7 +3525,7 @@
       <c r="C59" t="s">
         <v>76</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" s="20" t="s">
         <v>96</v>
       </c>
       <c r="E59">
@@ -3508,11 +3537,11 @@
       <c r="G59" t="b">
         <v>1</v>
       </c>
-      <c r="I59" s="21" t="str">
+      <c r="I59" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J59" s="21" t="str">
+      <c r="J59" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3527,7 +3556,7 @@
       <c r="C60" t="s">
         <v>78</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="20" t="s">
         <v>96</v>
       </c>
       <c r="E60">
@@ -3539,11 +3568,11 @@
       <c r="G60" t="b">
         <v>1</v>
       </c>
-      <c r="I60" s="21" t="str">
+      <c r="I60" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J60" s="21" t="str">
+      <c r="J60" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3570,11 +3599,11 @@
       <c r="G61" t="b">
         <v>1</v>
       </c>
-      <c r="I61" s="21" t="str">
+      <c r="I61" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J61" s="21" t="str">
+      <c r="J61" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3592,7 +3621,7 @@
       <c r="D62" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="17">
         <v>50</v>
       </c>
       <c r="F62" t="s">
@@ -3604,11 +3633,11 @@
       <c r="H62" t="s">
         <v>110</v>
       </c>
-      <c r="I62" s="21" t="str">
+      <c r="I62" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J62" s="21" t="str">
+      <c r="J62" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3635,11 +3664,11 @@
       <c r="G63" t="b">
         <v>1</v>
       </c>
-      <c r="I63" s="21" t="str">
+      <c r="I63" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J63" s="21" t="str">
+      <c r="J63" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3666,11 +3695,11 @@
       <c r="G64" t="b">
         <v>1</v>
       </c>
-      <c r="I64" s="21" t="str">
+      <c r="I64" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J64" s="21" t="str">
+      <c r="J64" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3697,11 +3726,11 @@
       <c r="G65" t="b">
         <v>1</v>
       </c>
-      <c r="I65" s="21" t="str">
+      <c r="I65" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J65" s="21" t="str">
+      <c r="J65" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3728,11 +3757,11 @@
       <c r="G66" t="b">
         <v>1</v>
       </c>
-      <c r="I66" s="21" t="str">
+      <c r="I66" s="19" t="str">
         <f t="shared" si="0"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J66" s="21" t="str">
+      <c r="J66" s="19" t="str">
         <f t="shared" si="1"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3762,11 +3791,11 @@
       <c r="H67" t="s">
         <v>109</v>
       </c>
-      <c r="I67" s="21" t="str">
+      <c r="I67" s="19" t="str">
         <f t="shared" ref="I67:I130" si="3">B67</f>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J67" s="21" t="str">
+      <c r="J67" s="19" t="str">
         <f t="shared" ref="J67:J130" si="4">B67</f>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3796,51 +3825,51 @@
       <c r="H68" t="s">
         <v>117</v>
       </c>
-      <c r="I68" s="21" t="str">
+      <c r="I68" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J68" s="21" t="str">
+      <c r="J68" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-LoElev</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
+      <c r="A69" t="s">
         <v>53</v>
       </c>
       <c r="B69" t="s">
         <v>54</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" t="s">
         <v>106</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E69" s="19">
+      <c r="E69" s="8">
         <v>10</v>
       </c>
-      <c r="F69" s="13" t="s">
+      <c r="F69" t="s">
         <v>107</v>
       </c>
-      <c r="G69" s="13" t="b">
+      <c r="G69" t="b">
         <v>1</v>
       </c>
       <c r="H69" t="s">
         <v>117</v>
       </c>
-      <c r="I69" s="21" t="str">
+      <c r="I69" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J69" s="21" t="str">
+      <c r="J69" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-LoElev</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
+      <c r="A70" t="s">
         <v>53</v>
       </c>
       <c r="B70" t="s">
@@ -3849,26 +3878,26 @@
       <c r="C70" t="s">
         <v>113</v>
       </c>
-      <c r="D70" s="19" t="s">
+      <c r="D70" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E70" s="19">
+      <c r="E70" s="8">
         <v>10</v>
       </c>
-      <c r="F70" s="13" t="s">
+      <c r="F70" t="s">
         <v>108</v>
       </c>
-      <c r="G70" s="13" t="b">
+      <c r="G70" t="b">
         <v>1</v>
       </c>
       <c r="H70" t="s">
         <v>117</v>
       </c>
-      <c r="I70" s="21" t="str">
+      <c r="I70" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J70" s="21" t="str">
+      <c r="J70" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -3886,7 +3915,7 @@
       <c r="D71" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E71" s="23">
+      <c r="E71" s="21">
         <v>8</v>
       </c>
       <c r="F71" t="s">
@@ -3895,11 +3924,11 @@
       <c r="G71" t="b">
         <v>0</v>
       </c>
-      <c r="I71" s="21" t="str">
+      <c r="I71" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J71" s="21" t="str">
+      <c r="J71" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -3926,11 +3955,11 @@
       <c r="G72" t="b">
         <v>0</v>
       </c>
-      <c r="I72" s="21" t="str">
+      <c r="I72" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J72" s="21" t="str">
+      <c r="J72" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -3957,11 +3986,11 @@
       <c r="G73" t="b">
         <v>0</v>
       </c>
-      <c r="I73" s="21" t="str">
+      <c r="I73" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J73" s="21" t="str">
+      <c r="J73" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -3988,11 +4017,11 @@
       <c r="G74" t="b">
         <v>0</v>
       </c>
-      <c r="I74" s="21" t="str">
+      <c r="I74" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J74" s="21" t="str">
+      <c r="J74" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4019,11 +4048,11 @@
       <c r="G75" t="b">
         <v>0</v>
       </c>
-      <c r="I75" s="21" t="str">
+      <c r="I75" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J75" s="21" t="str">
+      <c r="J75" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4050,11 +4079,11 @@
       <c r="G76" t="b">
         <v>0</v>
       </c>
-      <c r="I76" s="21" t="str">
+      <c r="I76" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J76" s="21" t="str">
+      <c r="J76" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4081,11 +4110,11 @@
       <c r="G77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" s="21" t="str">
+      <c r="I77" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J77" s="21" t="str">
+      <c r="J77" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4112,11 +4141,11 @@
       <c r="G78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" s="21" t="str">
+      <c r="I78" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J78" s="21" t="str">
+      <c r="J78" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4143,11 +4172,11 @@
       <c r="G79" t="b">
         <v>1</v>
       </c>
-      <c r="I79" s="21" t="str">
+      <c r="I79" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J79" s="21" t="str">
+      <c r="J79" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4174,11 +4203,11 @@
       <c r="G80" t="b">
         <v>1</v>
       </c>
-      <c r="I80" s="21" t="str">
+      <c r="I80" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J80" s="21" t="str">
+      <c r="J80" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4205,11 +4234,11 @@
       <c r="G81" t="b">
         <v>0</v>
       </c>
-      <c r="I81" s="21" t="str">
+      <c r="I81" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J81" s="21" t="str">
+      <c r="J81" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4236,11 +4265,11 @@
       <c r="G82" t="b">
         <v>0</v>
       </c>
-      <c r="I82" s="21" t="str">
+      <c r="I82" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J82" s="21" t="str">
+      <c r="J82" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4267,11 +4296,11 @@
       <c r="G83" t="b">
         <v>1</v>
       </c>
-      <c r="I83" s="21" t="str">
+      <c r="I83" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J83" s="21" t="str">
+      <c r="J83" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4298,11 +4327,11 @@
       <c r="G84" t="b">
         <v>1</v>
       </c>
-      <c r="I84" s="21" t="str">
+      <c r="I84" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J84" s="21" t="str">
+      <c r="J84" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4329,11 +4358,11 @@
       <c r="G85" t="b">
         <v>1</v>
       </c>
-      <c r="I85" s="21" t="str">
+      <c r="I85" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J85" s="21" t="str">
+      <c r="J85" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4360,11 +4389,11 @@
       <c r="G86" t="b">
         <v>1</v>
       </c>
-      <c r="I86" s="21" t="str">
+      <c r="I86" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J86" s="21" t="str">
+      <c r="J86" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4391,11 +4420,11 @@
       <c r="G87" t="b">
         <v>1</v>
       </c>
-      <c r="I87" s="21" t="str">
+      <c r="I87" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J87" s="21" t="str">
+      <c r="J87" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4422,11 +4451,11 @@
       <c r="G88" t="b">
         <v>1</v>
       </c>
-      <c r="I88" s="21" t="str">
+      <c r="I88" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J88" s="21" t="str">
+      <c r="J88" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4453,11 +4482,11 @@
       <c r="G89" t="b">
         <v>1</v>
       </c>
-      <c r="I89" s="21" t="str">
+      <c r="I89" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J89" s="21" t="str">
+      <c r="J89" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4484,11 +4513,11 @@
       <c r="G90" t="b">
         <v>1</v>
       </c>
-      <c r="I90" s="21" t="str">
+      <c r="I90" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J90" s="21" t="str">
+      <c r="J90" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4515,11 +4544,11 @@
       <c r="G91" t="b">
         <v>1</v>
       </c>
-      <c r="I91" s="21" t="str">
+      <c r="I91" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J91" s="21" t="str">
+      <c r="J91" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4546,11 +4575,11 @@
       <c r="G92" t="b">
         <v>1</v>
       </c>
-      <c r="I92" s="21" t="str">
+      <c r="I92" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J92" s="21" t="str">
+      <c r="J92" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4577,11 +4606,11 @@
       <c r="G93" t="b">
         <v>1</v>
       </c>
-      <c r="I93" s="21" t="str">
+      <c r="I93" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J93" s="21" t="str">
+      <c r="J93" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4608,11 +4637,11 @@
       <c r="G94" t="b">
         <v>1</v>
       </c>
-      <c r="I94" s="21" t="str">
+      <c r="I94" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J94" s="21" t="str">
+      <c r="J94" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4639,11 +4668,11 @@
       <c r="G95" t="b">
         <v>1</v>
       </c>
-      <c r="I95" s="21" t="str">
+      <c r="I95" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J95" s="21" t="str">
+      <c r="J95" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4670,11 +4699,11 @@
       <c r="G96" t="b">
         <v>1</v>
       </c>
-      <c r="I96" s="21" t="str">
+      <c r="I96" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J96" s="21" t="str">
+      <c r="J96" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4701,11 +4730,11 @@
       <c r="G97" t="b">
         <v>1</v>
       </c>
-      <c r="I97" s="21" t="str">
+      <c r="I97" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J97" s="21" t="str">
+      <c r="J97" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4732,11 +4761,11 @@
       <c r="G98" t="b">
         <v>1</v>
       </c>
-      <c r="I98" s="21" t="str">
+      <c r="I98" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J98" s="21" t="str">
+      <c r="J98" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4763,11 +4792,11 @@
       <c r="G99" t="b">
         <v>1</v>
       </c>
-      <c r="I99" s="21" t="str">
+      <c r="I99" s="19" t="str">
         <f t="shared" si="3"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J99" s="21" t="str">
+      <c r="J99" s="19" t="str">
         <f t="shared" si="4"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -4797,11 +4826,11 @@
       <c r="H100" t="s">
         <v>120</v>
       </c>
-      <c r="I100" s="21" t="str">
+      <c r="I100" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J100" s="21" t="str">
+      <c r="J100" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -4831,11 +4860,11 @@
       <c r="H101" t="s">
         <v>118</v>
       </c>
-      <c r="I101" s="21" t="str">
+      <c r="I101" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J101" s="21" t="str">
+      <c r="J101" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -4865,11 +4894,11 @@
       <c r="H102" t="s">
         <v>118</v>
       </c>
-      <c r="I102" s="21" t="str">
+      <c r="I102" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J102" s="21" t="str">
+      <c r="J102" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -4899,11 +4928,11 @@
       <c r="H103" t="s">
         <v>118</v>
       </c>
-      <c r="I103" s="21" t="str">
+      <c r="I103" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J103" s="21" t="str">
+      <c r="J103" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -4933,11 +4962,11 @@
       <c r="H104" t="s">
         <v>118</v>
       </c>
-      <c r="I104" s="21" t="str">
+      <c r="I104" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J104" s="21" t="str">
+      <c r="J104" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -4967,11 +4996,11 @@
       <c r="H105" t="s">
         <v>118</v>
       </c>
-      <c r="I105" s="21" t="str">
+      <c r="I105" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J105" s="21" t="str">
+      <c r="J105" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5001,11 +5030,11 @@
       <c r="H106" t="s">
         <v>118</v>
       </c>
-      <c r="I106" s="21" t="str">
+      <c r="I106" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J106" s="21" t="str">
+      <c r="J106" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5035,11 +5064,11 @@
       <c r="H107" t="s">
         <v>118</v>
       </c>
-      <c r="I107" s="21" t="str">
+      <c r="I107" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J107" s="21" t="str">
+      <c r="J107" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5069,11 +5098,11 @@
       <c r="H108" t="s">
         <v>118</v>
       </c>
-      <c r="I108" s="21" t="str">
+      <c r="I108" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J108" s="21" t="str">
+      <c r="J108" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5103,11 +5132,11 @@
       <c r="H109" t="s">
         <v>118</v>
       </c>
-      <c r="I109" s="21" t="str">
+      <c r="I109" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J109" s="21" t="str">
+      <c r="J109" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5137,11 +5166,11 @@
       <c r="H110" t="s">
         <v>118</v>
       </c>
-      <c r="I110" s="21" t="str">
+      <c r="I110" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J110" s="21" t="str">
+      <c r="J110" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5171,11 +5200,11 @@
       <c r="H111" t="s">
         <v>118</v>
       </c>
-      <c r="I111" s="21" t="str">
+      <c r="I111" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J111" s="21" t="str">
+      <c r="J111" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5205,11 +5234,11 @@
       <c r="H112" t="s">
         <v>118</v>
       </c>
-      <c r="I112" s="21" t="str">
+      <c r="I112" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J112" s="21" t="str">
+      <c r="J112" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5239,11 +5268,11 @@
       <c r="H113" t="s">
         <v>118</v>
       </c>
-      <c r="I113" s="21" t="str">
+      <c r="I113" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J113" s="21" t="str">
+      <c r="J113" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5273,11 +5302,11 @@
       <c r="H114" t="s">
         <v>118</v>
       </c>
-      <c r="I114" s="21" t="str">
+      <c r="I114" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J114" s="21" t="str">
+      <c r="J114" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5307,11 +5336,11 @@
       <c r="H115" t="s">
         <v>118</v>
       </c>
-      <c r="I115" s="21" t="str">
+      <c r="I115" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J115" s="21" t="str">
+      <c r="J115" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5341,11 +5370,11 @@
       <c r="H116" t="s">
         <v>118</v>
       </c>
-      <c r="I116" s="21" t="str">
+      <c r="I116" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J116" s="21" t="str">
+      <c r="J116" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5375,11 +5404,11 @@
       <c r="H117" t="s">
         <v>118</v>
       </c>
-      <c r="I117" s="21" t="str">
+      <c r="I117" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J117" s="21" t="str">
+      <c r="J117" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5409,11 +5438,11 @@
       <c r="H118" t="s">
         <v>118</v>
       </c>
-      <c r="I118" s="21" t="str">
+      <c r="I118" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J118" s="21" t="str">
+      <c r="J118" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5443,11 +5472,11 @@
       <c r="H119" t="s">
         <v>118</v>
       </c>
-      <c r="I119" s="21" t="str">
+      <c r="I119" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J119" s="21" t="str">
+      <c r="J119" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5477,11 +5506,11 @@
       <c r="H120" t="s">
         <v>118</v>
       </c>
-      <c r="I120" s="21" t="str">
+      <c r="I120" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J120" s="21" t="str">
+      <c r="J120" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5511,11 +5540,11 @@
       <c r="H121" t="s">
         <v>118</v>
       </c>
-      <c r="I121" s="21" t="str">
+      <c r="I121" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J121" s="21" t="str">
+      <c r="J121" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5545,11 +5574,11 @@
       <c r="H122" t="s">
         <v>118</v>
       </c>
-      <c r="I122" s="21" t="str">
+      <c r="I122" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J122" s="21" t="str">
+      <c r="J122" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5579,11 +5608,11 @@
       <c r="H123" t="s">
         <v>118</v>
       </c>
-      <c r="I123" s="21" t="str">
+      <c r="I123" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J123" s="21" t="str">
+      <c r="J123" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5613,11 +5642,11 @@
       <c r="H124" t="s">
         <v>118</v>
       </c>
-      <c r="I124" s="21" t="str">
+      <c r="I124" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J124" s="21" t="str">
+      <c r="J124" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5647,11 +5676,11 @@
       <c r="H125" t="s">
         <v>118</v>
       </c>
-      <c r="I125" s="21" t="str">
+      <c r="I125" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J125" s="21" t="str">
+      <c r="J125" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5681,11 +5710,11 @@
       <c r="H126" t="s">
         <v>118</v>
       </c>
-      <c r="I126" s="21" t="str">
+      <c r="I126" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J126" s="21" t="str">
+      <c r="J126" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -5715,16 +5744,16 @@
       <c r="H127" t="s">
         <v>118</v>
       </c>
-      <c r="I127" s="21" t="str">
+      <c r="I127" s="19" t="str">
         <f t="shared" si="3"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J127" s="21" t="str">
+      <c r="J127" s="19" t="str">
         <f t="shared" si="4"/>
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>123</v>
       </c>
@@ -5737,7 +5766,7 @@
       <c r="D128" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E128" s="23">
+      <c r="E128" s="21">
         <v>450</v>
       </c>
       <c r="F128" t="s">
@@ -5746,16 +5775,16 @@
       <c r="G128" t="b">
         <v>1</v>
       </c>
-      <c r="I128" s="21" t="str">
+      <c r="I128" s="19" t="str">
         <f t="shared" si="3"/>
         <v>ORWA</v>
       </c>
-      <c r="J128" s="21" t="str">
+      <c r="J128" s="19" t="str">
         <f t="shared" si="4"/>
         <v>ORWA</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>123</v>
       </c>
@@ -5777,19 +5806,19 @@
       <c r="G129" t="b">
         <v>1</v>
       </c>
-      <c r="H129" s="24">
+      <c r="H129" s="22">
         <v>45082</v>
       </c>
-      <c r="I129" s="21" t="str">
+      <c r="I129" s="19" t="str">
         <f t="shared" si="3"/>
         <v>ORWA</v>
       </c>
-      <c r="J129" s="21" t="str">
+      <c r="J129" s="19" t="str">
         <f t="shared" si="4"/>
         <v>ORWA</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>123</v>
       </c>
@@ -5811,19 +5840,19 @@
       <c r="G130" t="b">
         <v>1</v>
       </c>
-      <c r="H130" s="24">
+      <c r="H130" s="22">
         <v>45082</v>
       </c>
-      <c r="I130" s="21" t="str">
+      <c r="I130" s="19" t="str">
         <f t="shared" si="3"/>
         <v>ORWA</v>
       </c>
-      <c r="J130" s="21" t="str">
+      <c r="J130" s="19" t="str">
         <f t="shared" si="4"/>
         <v>ORWA</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>123</v>
       </c>
@@ -5845,19 +5874,19 @@
       <c r="G131" t="b">
         <v>1</v>
       </c>
-      <c r="H131" s="24">
+      <c r="H131" s="22">
         <v>45082</v>
       </c>
-      <c r="I131" s="21" t="str">
+      <c r="I131" s="19" t="str">
         <f t="shared" ref="I131:I135" si="5">B131</f>
         <v>ORWA</v>
       </c>
-      <c r="J131" s="21" t="str">
+      <c r="J131" s="19" t="str">
         <f t="shared" ref="J131:J135" si="6">B131</f>
         <v>ORWA</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>123</v>
       </c>
@@ -5879,14 +5908,14 @@
       <c r="G132" t="b">
         <v>1</v>
       </c>
-      <c r="H132" s="24">
+      <c r="H132" s="22">
         <v>45082</v>
       </c>
-      <c r="I132" s="21" t="str">
+      <c r="I132" s="19" t="str">
         <f t="shared" si="5"/>
         <v>ORWA</v>
       </c>
-      <c r="J132" s="21" t="str">
+      <c r="J132" s="19" t="str">
         <f t="shared" si="6"/>
         <v>ORWA</v>
       </c>
@@ -5898,7 +5927,7 @@
       <c r="B133" t="s">
         <v>103</v>
       </c>
-      <c r="C133" s="25" t="s">
+      <c r="C133" s="23" t="s">
         <v>151</v>
       </c>
       <c r="D133" s="8" t="s">
@@ -5913,14 +5942,14 @@
       <c r="G133" t="b">
         <v>0</v>
       </c>
-      <c r="H133" s="24">
+      <c r="H133" s="22">
         <v>45083</v>
       </c>
-      <c r="I133" s="21" t="str">
+      <c r="I133" s="19" t="str">
         <f t="shared" si="5"/>
         <v>HiGrad-HiElev</v>
       </c>
-      <c r="J133" s="21" t="str">
+      <c r="J133" s="19" t="str">
         <f t="shared" si="6"/>
         <v>HiGrad-HiElev</v>
       </c>
@@ -5932,7 +5961,7 @@
       <c r="B134" t="s">
         <v>54</v>
       </c>
-      <c r="C134" s="25" t="s">
+      <c r="C134" s="23" t="s">
         <v>151</v>
       </c>
       <c r="D134" s="8" t="s">
@@ -5947,14 +5976,14 @@
       <c r="G134" t="b">
         <v>0</v>
       </c>
-      <c r="H134" s="24">
+      <c r="H134" s="22">
         <v>45083</v>
       </c>
-      <c r="I134" s="21" t="str">
+      <c r="I134" s="19" t="str">
         <f t="shared" si="5"/>
         <v>HiGrad-LoElev</v>
       </c>
-      <c r="J134" s="21" t="str">
+      <c r="J134" s="19" t="str">
         <f t="shared" si="6"/>
         <v>HiGrad-LoElev</v>
       </c>
@@ -5966,7 +5995,7 @@
       <c r="B135" t="s">
         <v>119</v>
       </c>
-      <c r="C135" s="25" t="s">
+      <c r="C135" s="23" t="s">
         <v>151</v>
       </c>
       <c r="D135" s="8" t="s">
@@ -5981,14 +6010,14 @@
       <c r="G135" t="b">
         <v>0</v>
       </c>
-      <c r="H135" s="24">
+      <c r="H135" s="22">
         <v>45083</v>
       </c>
-      <c r="I135" s="21" t="str">
+      <c r="I135" s="19" t="str">
         <f t="shared" si="5"/>
         <v>LoGrad-LoElev</v>
       </c>
-      <c r="J135" s="21" t="str">
+      <c r="J135" s="19" t="str">
         <f t="shared" si="6"/>
         <v>LoGrad-LoElev</v>
       </c>
@@ -6000,7 +6029,7 @@
       <c r="B136" t="s">
         <v>155</v>
       </c>
-      <c r="C136" s="26" t="s">
+      <c r="C136" s="24" t="s">
         <v>157</v>
       </c>
       <c r="D136" s="8" t="s">
@@ -6015,14 +6044,14 @@
       <c r="G136" t="b">
         <v>1</v>
       </c>
-      <c r="H136" s="24" t="s">
+      <c r="H136" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="I136" s="21" t="str">
+      <c r="I136" s="19" t="str">
         <f t="shared" ref="I136:I137" si="7">B136</f>
         <v>CREMP_Keys</v>
       </c>
-      <c r="J136" s="21" t="str">
+      <c r="J136" s="19" t="str">
         <f t="shared" ref="J136:J137" si="8">B136</f>
         <v>CREMP_Keys</v>
       </c>
@@ -6034,7 +6063,7 @@
       <c r="B137" t="s">
         <v>156</v>
       </c>
-      <c r="C137" s="26" t="s">
+      <c r="C137" s="24" t="s">
         <v>157</v>
       </c>
       <c r="D137" s="8" t="s">
@@ -6049,67 +6078,742 @@
       <c r="G137" t="b">
         <v>1</v>
       </c>
-      <c r="H137" s="24" t="s">
+      <c r="H137" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="I137" s="21" t="str">
+      <c r="I137" s="19" t="str">
         <f t="shared" si="7"/>
         <v>NOT_CREMP_Keys</v>
       </c>
-      <c r="J137" s="21" t="str">
+      <c r="J137" s="19" t="str">
         <f t="shared" si="8"/>
         <v>NOT_CREMP_Keys</v>
       </c>
     </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>162</v>
+      </c>
+      <c r="B138" t="s">
+        <v>163</v>
+      </c>
+      <c r="C138" t="s">
+        <v>14</v>
+      </c>
+      <c r="D138" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138">
+        <v>150</v>
+      </c>
+      <c r="F138" t="s">
+        <v>38</v>
+      </c>
+      <c r="G138" t="b">
+        <v>1</v>
+      </c>
+      <c r="I138" t="s">
+        <v>162</v>
+      </c>
+      <c r="J138" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>162</v>
+      </c>
+      <c r="B139" t="s">
+        <v>164</v>
+      </c>
+      <c r="C139" t="s">
+        <v>14</v>
+      </c>
+      <c r="D139" t="s">
+        <v>16</v>
+      </c>
+      <c r="E139">
+        <v>150</v>
+      </c>
+      <c r="F139" t="s">
+        <v>38</v>
+      </c>
+      <c r="G139" t="b">
+        <v>1</v>
+      </c>
+      <c r="I139" t="s">
+        <v>162</v>
+      </c>
+      <c r="J139" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>162</v>
+      </c>
+      <c r="B140" t="s">
+        <v>165</v>
+      </c>
+      <c r="C140" t="s">
+        <v>14</v>
+      </c>
+      <c r="D140" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140">
+        <v>150</v>
+      </c>
+      <c r="F140" t="s">
+        <v>38</v>
+      </c>
+      <c r="G140" t="b">
+        <v>1</v>
+      </c>
+      <c r="I140" t="s">
+        <v>162</v>
+      </c>
+      <c r="J140" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>162</v>
+      </c>
+      <c r="B141" t="s">
+        <v>166</v>
+      </c>
+      <c r="C141" t="s">
+        <v>14</v>
+      </c>
+      <c r="D141" t="s">
+        <v>16</v>
+      </c>
+      <c r="E141">
+        <v>150</v>
+      </c>
+      <c r="F141" t="s">
+        <v>38</v>
+      </c>
+      <c r="G141" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" t="s">
+        <v>162</v>
+      </c>
+      <c r="J141" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>162</v>
+      </c>
+      <c r="B142" t="s">
+        <v>163</v>
+      </c>
+      <c r="C142" t="s">
+        <v>167</v>
+      </c>
+      <c r="D142" t="s">
+        <v>16</v>
+      </c>
+      <c r="E142">
+        <v>30</v>
+      </c>
+      <c r="F142" t="s">
+        <v>41</v>
+      </c>
+      <c r="G142" t="b">
+        <v>0</v>
+      </c>
+      <c r="I142" t="s">
+        <v>162</v>
+      </c>
+      <c r="J142" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>162</v>
+      </c>
+      <c r="B143" t="s">
+        <v>165</v>
+      </c>
+      <c r="C143" t="s">
+        <v>167</v>
+      </c>
+      <c r="D143" t="s">
+        <v>16</v>
+      </c>
+      <c r="E143">
+        <v>30</v>
+      </c>
+      <c r="F143" t="s">
+        <v>41</v>
+      </c>
+      <c r="G143" t="b">
+        <v>0</v>
+      </c>
+      <c r="I143" t="s">
+        <v>162</v>
+      </c>
+      <c r="J143" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>162</v>
+      </c>
+      <c r="B144" t="s">
+        <v>163</v>
+      </c>
+      <c r="C144" t="s">
+        <v>168</v>
+      </c>
+      <c r="D144" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144">
+        <v>11.6</v>
+      </c>
+      <c r="F144" t="s">
+        <v>41</v>
+      </c>
+      <c r="G144" t="b">
+        <v>0</v>
+      </c>
+      <c r="I144" t="s">
+        <v>162</v>
+      </c>
+      <c r="J144" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B145" t="s">
+        <v>165</v>
+      </c>
+      <c r="C145" t="s">
+        <v>168</v>
+      </c>
+      <c r="D145" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145">
+        <v>11.6</v>
+      </c>
+      <c r="F145" t="s">
+        <v>41</v>
+      </c>
+      <c r="G145" t="b">
+        <v>0</v>
+      </c>
+      <c r="I145" t="s">
+        <v>162</v>
+      </c>
+      <c r="J145" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>162</v>
+      </c>
+      <c r="B146" t="s">
+        <v>163</v>
+      </c>
+      <c r="C146" t="s">
+        <v>169</v>
+      </c>
+      <c r="D146" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146">
+        <v>70</v>
+      </c>
+      <c r="F146" t="s">
+        <v>170</v>
+      </c>
+      <c r="G146" t="b">
+        <v>1</v>
+      </c>
+      <c r="I146" t="s">
+        <v>162</v>
+      </c>
+      <c r="J146" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>162</v>
+      </c>
+      <c r="B147" t="s">
+        <v>164</v>
+      </c>
+      <c r="C147" t="s">
+        <v>169</v>
+      </c>
+      <c r="D147" t="s">
+        <v>17</v>
+      </c>
+      <c r="E147">
+        <v>70</v>
+      </c>
+      <c r="F147" t="s">
+        <v>170</v>
+      </c>
+      <c r="G147" t="b">
+        <v>1</v>
+      </c>
+      <c r="I147" t="s">
+        <v>162</v>
+      </c>
+      <c r="J147" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>162</v>
+      </c>
+      <c r="B148" t="s">
+        <v>165</v>
+      </c>
+      <c r="C148" t="s">
+        <v>169</v>
+      </c>
+      <c r="D148" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148">
+        <v>70</v>
+      </c>
+      <c r="F148" t="s">
+        <v>170</v>
+      </c>
+      <c r="G148" t="b">
+        <v>1</v>
+      </c>
+      <c r="I148" t="s">
+        <v>162</v>
+      </c>
+      <c r="J148" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>162</v>
+      </c>
+      <c r="B149" t="s">
+        <v>166</v>
+      </c>
+      <c r="C149" t="s">
+        <v>169</v>
+      </c>
+      <c r="D149" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149">
+        <v>70</v>
+      </c>
+      <c r="F149" t="s">
+        <v>170</v>
+      </c>
+      <c r="G149" t="b">
+        <v>1</v>
+      </c>
+      <c r="I149" t="s">
+        <v>162</v>
+      </c>
+      <c r="J149" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>162</v>
+      </c>
+      <c r="B150" t="s">
+        <v>163</v>
+      </c>
+      <c r="C150" t="s">
+        <v>171</v>
+      </c>
+      <c r="D150" t="s">
+        <v>15</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+      <c r="F150" t="s">
+        <v>172</v>
+      </c>
+      <c r="G150" t="b">
+        <v>1</v>
+      </c>
+      <c r="I150" t="s">
+        <v>162</v>
+      </c>
+      <c r="J150" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>162</v>
+      </c>
+      <c r="B151" t="s">
+        <v>164</v>
+      </c>
+      <c r="C151" t="s">
+        <v>171</v>
+      </c>
+      <c r="D151" t="s">
+        <v>15</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+      <c r="F151" t="s">
+        <v>172</v>
+      </c>
+      <c r="G151" t="b">
+        <v>1</v>
+      </c>
+      <c r="I151" t="s">
+        <v>162</v>
+      </c>
+      <c r="J151" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>162</v>
+      </c>
+      <c r="B152" t="s">
+        <v>165</v>
+      </c>
+      <c r="C152" t="s">
+        <v>171</v>
+      </c>
+      <c r="D152" t="s">
+        <v>15</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="F152" t="s">
+        <v>172</v>
+      </c>
+      <c r="G152" t="b">
+        <v>1</v>
+      </c>
+      <c r="I152" t="s">
+        <v>162</v>
+      </c>
+      <c r="J152" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>162</v>
+      </c>
+      <c r="B153" t="s">
+        <v>166</v>
+      </c>
+      <c r="C153" t="s">
+        <v>171</v>
+      </c>
+      <c r="D153" t="s">
+        <v>15</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153" t="s">
+        <v>172</v>
+      </c>
+      <c r="G153" t="b">
+        <v>1</v>
+      </c>
+      <c r="I153" t="s">
+        <v>162</v>
+      </c>
+      <c r="J153" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>162</v>
+      </c>
+      <c r="B154" t="s">
+        <v>163</v>
+      </c>
+      <c r="C154" t="s">
+        <v>173</v>
+      </c>
+      <c r="D154" t="s">
+        <v>15</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154" t="s">
+        <v>174</v>
+      </c>
+      <c r="G154" t="b">
+        <v>1</v>
+      </c>
+      <c r="I154" t="s">
+        <v>162</v>
+      </c>
+      <c r="J154" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" t="s">
+        <v>164</v>
+      </c>
+      <c r="C155" t="s">
+        <v>173</v>
+      </c>
+      <c r="D155" t="s">
+        <v>15</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+      <c r="F155" t="s">
+        <v>174</v>
+      </c>
+      <c r="G155" t="b">
+        <v>1</v>
+      </c>
+      <c r="I155" t="s">
+        <v>162</v>
+      </c>
+      <c r="J155" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" t="s">
+        <v>165</v>
+      </c>
+      <c r="C156" t="s">
+        <v>173</v>
+      </c>
+      <c r="D156" t="s">
+        <v>15</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="F156" t="s">
+        <v>174</v>
+      </c>
+      <c r="G156" t="b">
+        <v>1</v>
+      </c>
+      <c r="I156" t="s">
+        <v>162</v>
+      </c>
+      <c r="J156" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>162</v>
+      </c>
+      <c r="B157" t="s">
+        <v>166</v>
+      </c>
+      <c r="C157" t="s">
+        <v>173</v>
+      </c>
+      <c r="D157" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="F157" t="s">
+        <v>174</v>
+      </c>
+      <c r="G157" t="b">
+        <v>1</v>
+      </c>
+      <c r="I157" t="s">
+        <v>162</v>
+      </c>
+      <c r="J157" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>162</v>
+      </c>
+      <c r="B158" t="s">
+        <v>163</v>
+      </c>
+      <c r="C158" t="s">
+        <v>175</v>
+      </c>
+      <c r="D158" t="s">
+        <v>15</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158" t="s">
+        <v>176</v>
+      </c>
+      <c r="G158" t="b">
+        <v>1</v>
+      </c>
+      <c r="I158" t="s">
+        <v>162</v>
+      </c>
+      <c r="J158" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159" t="s">
+        <v>164</v>
+      </c>
+      <c r="C159" t="s">
+        <v>175</v>
+      </c>
+      <c r="D159" t="s">
+        <v>15</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+      <c r="F159" t="s">
+        <v>176</v>
+      </c>
+      <c r="G159" t="b">
+        <v>1</v>
+      </c>
+      <c r="I159" t="s">
+        <v>162</v>
+      </c>
+      <c r="J159" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>162</v>
+      </c>
+      <c r="B160" t="s">
+        <v>165</v>
+      </c>
+      <c r="C160" t="s">
+        <v>175</v>
+      </c>
+      <c r="D160" t="s">
+        <v>15</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="F160" t="s">
+        <v>176</v>
+      </c>
+      <c r="G160" t="b">
+        <v>1</v>
+      </c>
+      <c r="I160" t="s">
+        <v>162</v>
+      </c>
+      <c r="J160" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>162</v>
+      </c>
+      <c r="B161" t="s">
+        <v>166</v>
+      </c>
+      <c r="C161" t="s">
+        <v>175</v>
+      </c>
+      <c r="D161" t="s">
+        <v>15</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+      <c r="F161" t="s">
+        <v>176</v>
+      </c>
+      <c r="G161" t="b">
+        <v>1</v>
+      </c>
+      <c r="I161" t="s">
+        <v>162</v>
+      </c>
+      <c r="J161" t="s">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J132" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="BCG_MariNW_Bugs500ct"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="G2:G127 H100">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+  <autoFilter ref="A1:J132" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <conditionalFormatting sqref="C2:C66">
+    <cfRule type="expression" dxfId="5" priority="8">
+      <formula>$G2=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C128">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>$G128=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G153">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$G2=FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C66">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>$G3=FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H54">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H101:H127">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+  <conditionalFormatting sqref="H100:H127">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G128:G132">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C128">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>$G128=FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G133:G135">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G136:G137">
+  <conditionalFormatting sqref="G154:G161">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
